--- a/Course_Output.xlsx
+++ b/Course_Output.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="49">
   <si>
     <t>Course-ID</t>
   </si>
@@ -83,67 +83,82 @@
     <t>7:30-9:00</t>
   </si>
   <si>
-    <t>14:30-16:00</t>
+    <t>13:00-14:30</t>
   </si>
   <si>
     <t>Null</t>
   </si>
   <si>
+    <t>7:30 - 9:00</t>
+  </si>
+  <si>
+    <t>14:30 - 16:00</t>
+  </si>
+  <si>
     <t>Database Systems</t>
   </si>
   <si>
-    <t>Learn relational database and SQL</t>
+    <t>Learn relational databases and SQL</t>
   </si>
   <si>
     <t>Room B1</t>
   </si>
   <si>
-    <t>13:00-14:30</t>
+    <t>13:00 - 14:30</t>
+  </si>
+  <si>
+    <t>Network Security</t>
+  </si>
+  <si>
+    <t>Fundamentals of network security</t>
+  </si>
+  <si>
+    <t>Room C1</t>
+  </si>
+  <si>
+    <t>9:00 - 10:30</t>
+  </si>
+  <si>
+    <t>18:00 - 19:30</t>
+  </si>
+  <si>
+    <t>DevOps Fundamentals</t>
+  </si>
+  <si>
+    <t>Learn the core DevOps principles, CI/CD, and automation tools.</t>
+  </si>
+  <si>
+    <t>Room D1</t>
+  </si>
+  <si>
+    <t>Spring Boot Applications</t>
+  </si>
+  <si>
+    <t>Build modern Java applications using Spring Boot and Spring MVC.</t>
+  </si>
+  <si>
+    <t>Room E1</t>
   </si>
   <si>
     <t>Full Stack Web Development</t>
   </si>
   <si>
-    <t>Learn full stack development with React,Node.js,and Database</t>
+    <t>Learn full stack development with React, Node.js, and databases.</t>
   </si>
   <si>
     <t>Room F1</t>
   </si>
   <si>
-    <t>9:00-10:30</t>
-  </si>
-  <si>
-    <t>18:00-19:30</t>
-  </si>
-  <si>
-    <t>Network Security</t>
-  </si>
-  <si>
-    <t>Fundamentals of network security</t>
-  </si>
-  <si>
-    <t>Room C1</t>
-  </si>
-  <si>
-    <t>DevOps Fundamentals</t>
-  </si>
-  <si>
-    <t>Learn the core DevOps principles, CI/CD, and automation tools</t>
-  </si>
-  <si>
-    <t>Room D1</t>
-  </si>
-  <si>
-    <t>Spring Boot Applications</t>
-  </si>
-  <si>
-    <t>Build Modern Java application using Spring Boot</t>
-  </si>
-  <si>
-    <t>Room E1</t>
-  </si>
-  <si>
-    <t>16:00-17:30</t>
+    <t>16:00 - 17:30</t>
+  </si>
+  <si>
+    <t>Foundation</t>
+  </si>
+  <si>
+    <t>For basic</t>
+  </si>
+  <si>
+    <t>Room K1</t>
   </si>
 </sst>
 </file>
@@ -270,7 +285,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
       <alignment horizontal="center"/>
@@ -319,6 +334,27 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment wrapText="true"/>
@@ -344,7 +380,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:P7"/>
+  <dimension ref="A1:P14"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="19.53125" customWidth="true"/>
@@ -424,7 +460,7 @@
         <v>16</v>
       </c>
       <c r="C2" t="n" s="0">
-        <v>500.0</v>
+        <v>300.0</v>
       </c>
       <c r="D2" t="s" s="17">
         <v>17</v>
@@ -468,122 +504,120 @@
     </row>
     <row r="3">
       <c r="A3" t="n" s="0">
-        <v>2.0</v>
+        <v>1.0</v>
       </c>
       <c r="B3" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C3" t="n" s="0">
+        <v>300.0</v>
+      </c>
+      <c r="D3" t="s" s="18">
+        <v>17</v>
+      </c>
+      <c r="E3" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="F3" t="n" s="0">
+        <v>30.0</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="H3" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="I3" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="J3" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="K3" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="L3" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="M3" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="N3" t="s" s="0">
         <v>25</v>
       </c>
-      <c r="C3" t="n" s="0">
-        <v>700.0</v>
-      </c>
-      <c r="D3" t="s" s="18">
+      <c r="O3" t="s" s="0">
         <v>26</v>
       </c>
-      <c r="E3" t="n" s="0">
-        <v>4.0</v>
-      </c>
-      <c r="F3" t="n" s="0">
-        <v>25.0</v>
-      </c>
-      <c r="G3" t="s" s="0">
-        <v>18</v>
-      </c>
-      <c r="H3" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="I3" t="n" s="0">
-        <v>2.0</v>
-      </c>
-      <c r="J3" t="s" s="0">
-        <v>27</v>
-      </c>
-      <c r="K3" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="L3" t="n" s="0">
-        <v>2.0</v>
-      </c>
-      <c r="M3" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="N3" t="s" s="0">
-        <v>22</v>
-      </c>
-      <c r="O3" t="s" s="0">
-        <v>28</v>
-      </c>
-      <c r="P3" t="s" s="0">
-        <v>24</v>
-      </c>
+      <c r="P3" s="0"/>
     </row>
     <row r="4">
       <c r="A4" t="n" s="0">
-        <v>6.0</v>
+        <v>2.0</v>
       </c>
       <c r="B4" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="C4" t="n" s="0">
+        <v>700.0</v>
+      </c>
+      <c r="D4" t="s" s="19">
+        <v>28</v>
+      </c>
+      <c r="E4" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="F4" t="n" s="0">
+        <v>25.0</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="H4" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="I4" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="J4" t="s" s="0">
         <v>29</v>
       </c>
-      <c r="C4" t="n" s="0">
-        <v>900.0</v>
-      </c>
-      <c r="D4" t="s" s="19">
-        <v>30</v>
-      </c>
-      <c r="E4" t="n" s="0">
-        <v>5.0</v>
-      </c>
-      <c r="F4" t="n" s="0">
-        <v>30.0</v>
-      </c>
-      <c r="G4" t="s" s="0">
-        <v>18</v>
-      </c>
-      <c r="H4" t="s" s="0">
-        <v>19</v>
-      </c>
-      <c r="I4" t="n" s="0">
-        <v>3.0</v>
-      </c>
-      <c r="J4" t="s" s="0">
-        <v>31</v>
-      </c>
       <c r="K4" t="n" s="0">
         <v>1.0</v>
       </c>
       <c r="L4" t="n" s="0">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="M4" t="s" s="0">
         <v>21</v>
       </c>
       <c r="N4" t="s" s="0">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="O4" t="s" s="0">
-        <v>28</v>
+        <v>23</v>
       </c>
       <c r="P4" t="s" s="0">
-        <v>33</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n" s="0">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="B5" t="s" s="0">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="C5" t="n" s="0">
-        <v>800.0</v>
+        <v>700.0</v>
       </c>
       <c r="D5" t="s" s="20">
-        <v>35</v>
+        <v>28</v>
       </c>
       <c r="E5" t="n" s="0">
         <v>4.0</v>
       </c>
       <c r="F5" t="n" s="0">
-        <v>20.0</v>
+        <v>25.0</v>
       </c>
       <c r="G5" t="s" s="0">
         <v>18</v>
@@ -592,48 +626,46 @@
         <v>19</v>
       </c>
       <c r="I5" t="n" s="0">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="J5" t="s" s="0">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="K5" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="L5" t="n" s="0">
         <v>2.0</v>
       </c>
-      <c r="L5" t="n" s="0">
-        <v>1.0</v>
-      </c>
       <c r="M5" t="s" s="0">
         <v>21</v>
       </c>
       <c r="N5" t="s" s="0">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="O5" t="s" s="0">
-        <v>28</v>
-      </c>
-      <c r="P5" t="s" s="0">
-        <v>33</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="P5" s="0"/>
     </row>
     <row r="6">
       <c r="A6" t="n" s="0">
-        <v>4.0</v>
+        <v>3.0</v>
       </c>
       <c r="B6" t="s" s="0">
-        <v>37</v>
+        <v>31</v>
       </c>
       <c r="C6" t="n" s="0">
-        <v>750.0</v>
+        <v>800.0</v>
       </c>
       <c r="D6" t="s" s="21">
-        <v>38</v>
+        <v>32</v>
       </c>
       <c r="E6" t="n" s="0">
         <v>4.0</v>
       </c>
       <c r="F6" t="n" s="0">
-        <v>25.0</v>
+        <v>20.0</v>
       </c>
       <c r="G6" t="s" s="0">
         <v>18</v>
@@ -642,13 +674,13 @@
         <v>19</v>
       </c>
       <c r="I6" t="n" s="0">
-        <v>1.0</v>
+        <v>3.0</v>
       </c>
       <c r="J6" t="s" s="0">
-        <v>39</v>
+        <v>33</v>
       </c>
       <c r="K6" t="n" s="0">
-        <v>3.0</v>
+        <v>2.0</v>
       </c>
       <c r="L6" t="n" s="0">
         <v>1.0</v>
@@ -657,7 +689,7 @@
         <v>21</v>
       </c>
       <c r="N6" t="s" s="0">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="O6" t="s" s="0">
         <v>23</v>
@@ -668,16 +700,16 @@
     </row>
     <row r="7">
       <c r="A7" t="n" s="0">
-        <v>5.0</v>
+        <v>3.0</v>
       </c>
       <c r="B7" t="s" s="0">
-        <v>40</v>
+        <v>31</v>
       </c>
       <c r="C7" t="n" s="0">
         <v>800.0</v>
       </c>
       <c r="D7" t="s" s="22">
-        <v>41</v>
+        <v>32</v>
       </c>
       <c r="E7" t="n" s="0">
         <v>4.0</v>
@@ -692,27 +724,373 @@
         <v>19</v>
       </c>
       <c r="I7" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="J7" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="K7" t="n" s="0">
         <v>2.0</v>
       </c>
-      <c r="J7" t="s" s="0">
+      <c r="L7" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="M7" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="N7" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="O7" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="P7" t="s" s="0">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="C8" t="n" s="0">
+        <v>750.0</v>
+      </c>
+      <c r="D8" t="s" s="23">
+        <v>37</v>
+      </c>
+      <c r="E8" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="F8" t="n" s="0">
+        <v>25.0</v>
+      </c>
+      <c r="G8" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="H8" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="I8" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="J8" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="K8" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="L8" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="M8" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="N8" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="O8" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="P8" t="s" s="0">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>36</v>
+      </c>
+      <c r="C9" t="n" s="0">
+        <v>750.0</v>
+      </c>
+      <c r="D9" t="s" s="24">
+        <v>37</v>
+      </c>
+      <c r="E9" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="F9" t="n" s="0">
+        <v>25.0</v>
+      </c>
+      <c r="G9" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="H9" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="I9" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="J9" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="K9" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="L9" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="M9" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="N9" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="O9" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="P9" t="s" s="0">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="C10" t="n" s="0">
+        <v>800.0</v>
+      </c>
+      <c r="D10" t="s" s="25">
+        <v>40</v>
+      </c>
+      <c r="E10" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="F10" t="n" s="0">
+        <v>20.0</v>
+      </c>
+      <c r="G10" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="H10" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="I10" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="J10" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="K10" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="L10" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="M10" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="N10" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="O10" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="P10" s="0"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="C11" t="n" s="0">
+        <v>800.0</v>
+      </c>
+      <c r="D11" t="s" s="26">
+        <v>40</v>
+      </c>
+      <c r="E11" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="F11" t="n" s="0">
+        <v>20.0</v>
+      </c>
+      <c r="G11" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="H11" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="I11" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="J11" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="K11" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="L11" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="M11" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="N11" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="O11" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="P11" t="s" s="0">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="B12" t="s" s="0">
         <v>42</v>
       </c>
-      <c r="K7" t="n" s="0">
-        <v>4.0</v>
-      </c>
-      <c r="L7" t="n" s="0">
-        <v>1.0</v>
-      </c>
-      <c r="M7" t="s" s="0">
-        <v>21</v>
-      </c>
-      <c r="N7" t="s" s="0">
+      <c r="C12" t="n" s="0">
+        <v>900.0</v>
+      </c>
+      <c r="D12" t="s" s="27">
+        <v>43</v>
+      </c>
+      <c r="E12" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="F12" t="n" s="0">
+        <v>30.0</v>
+      </c>
+      <c r="G12" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="H12" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="I12" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="J12" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="K12" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="L12" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="M12" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="N12" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="O12" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="P12" s="0"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n" s="0">
+        <v>6.0</v>
+      </c>
+      <c r="B13" t="s" s="0">
+        <v>42</v>
+      </c>
+      <c r="C13" t="n" s="0">
+        <v>900.0</v>
+      </c>
+      <c r="D13" t="s" s="28">
+        <v>43</v>
+      </c>
+      <c r="E13" t="n" s="0">
+        <v>5.0</v>
+      </c>
+      <c r="F13" t="n" s="0">
+        <v>30.0</v>
+      </c>
+      <c r="G13" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="H13" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="I13" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="J13" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="K13" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="L13" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="M13" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="N13" t="s" s="0">
         <v>22</v>
       </c>
-      <c r="O7" t="s" s="0">
-        <v>43</v>
-      </c>
-      <c r="P7" t="s" s="0">
+      <c r="O13" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="P13" t="s" s="0">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n" s="0">
+        <v>9.0</v>
+      </c>
+      <c r="B14" t="s" s="0">
+        <v>46</v>
+      </c>
+      <c r="C14" t="n" s="0">
+        <v>400.0</v>
+      </c>
+      <c r="D14" t="s" s="29">
+        <v>47</v>
+      </c>
+      <c r="E14" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="F14" t="n" s="0">
+        <v>10.0</v>
+      </c>
+      <c r="G14" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="H14" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="I14" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="J14" t="s" s="0">
+        <v>48</v>
+      </c>
+      <c r="K14" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="L14" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="M14" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="N14" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="O14" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="P14" t="s" s="0">
         <v>24</v>
       </c>
     </row>

--- a/Course_Output.xlsx
+++ b/Course_Output.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="56">
   <si>
     <t>Course-ID</t>
   </si>
@@ -80,6 +80,12 @@
     <t>Monday to Friday</t>
   </si>
   <si>
+    <t>7:30 - 9:00</t>
+  </si>
+  <si>
+    <t>14:30 - 16:00</t>
+  </si>
+  <si>
     <t>7:30-9:00</t>
   </si>
   <si>
@@ -89,12 +95,6 @@
     <t>Null</t>
   </si>
   <si>
-    <t>7:30 - 9:00</t>
-  </si>
-  <si>
-    <t>14:30 - 16:00</t>
-  </si>
-  <si>
     <t>Database Systems</t>
   </si>
   <si>
@@ -159,6 +159,27 @@
   </si>
   <si>
     <t>Room K1</t>
+  </si>
+  <si>
+    <t>AI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Make ai work for us </t>
+  </si>
+  <si>
+    <t>Room Z1</t>
+  </si>
+  <si>
+    <t>flutter</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Make app work for us </t>
+  </si>
+  <si>
+    <t>2026-04-01</t>
+  </si>
+  <si>
+    <t>2026-08-01</t>
   </si>
 </sst>
 </file>
@@ -285,7 +306,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="30">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
       <alignment horizontal="center"/>
@@ -334,6 +355,12 @@
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <alignment wrapText="true"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment wrapText="true"/>
@@ -380,7 +407,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:P14"/>
+  <dimension ref="A1:P16"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="19.53125" customWidth="true"/>
@@ -498,9 +525,7 @@
       <c r="O2" t="s" s="0">
         <v>23</v>
       </c>
-      <c r="P2" t="s" s="0">
-        <v>24</v>
-      </c>
+      <c r="P2" s="0"/>
     </row>
     <row r="3">
       <c r="A3" t="n" s="0">
@@ -543,12 +568,14 @@
         <v>21</v>
       </c>
       <c r="N3" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="O3" t="s" s="0">
         <v>25</v>
       </c>
-      <c r="O3" t="s" s="0">
+      <c r="P3" t="s" s="0">
         <v>26</v>
       </c>
-      <c r="P3" s="0"/>
     </row>
     <row r="4">
       <c r="A4" t="n" s="0">
@@ -591,13 +618,13 @@
         <v>21</v>
       </c>
       <c r="N4" t="s" s="0">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="O4" t="s" s="0">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="P4" t="s" s="0">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="5">
@@ -641,7 +668,7 @@
         <v>21</v>
       </c>
       <c r="N5" t="s" s="0">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="O5" t="s" s="0">
         <v>30</v>
@@ -689,13 +716,13 @@
         <v>21</v>
       </c>
       <c r="N6" t="s" s="0">
-        <v>22</v>
+        <v>34</v>
       </c>
       <c r="O6" t="s" s="0">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="P6" t="s" s="0">
-        <v>24</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7">
@@ -739,13 +766,13 @@
         <v>21</v>
       </c>
       <c r="N7" t="s" s="0">
-        <v>34</v>
+        <v>24</v>
       </c>
       <c r="O7" t="s" s="0">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P7" t="s" s="0">
-        <v>35</v>
+        <v>26</v>
       </c>
     </row>
     <row r="8">
@@ -789,13 +816,13 @@
         <v>21</v>
       </c>
       <c r="N8" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="O8" t="s" s="0">
         <v>25</v>
       </c>
-      <c r="O8" t="s" s="0">
-        <v>30</v>
-      </c>
       <c r="P8" t="s" s="0">
-        <v>35</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9">
@@ -842,10 +869,10 @@
         <v>22</v>
       </c>
       <c r="O9" t="s" s="0">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="P9" t="s" s="0">
-        <v>24</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10">
@@ -892,7 +919,7 @@
         <v>34</v>
       </c>
       <c r="O10" t="s" s="0">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="P10" s="0"/>
     </row>
@@ -937,13 +964,13 @@
         <v>21</v>
       </c>
       <c r="N11" t="s" s="0">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="O11" t="s" s="0">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="P11" t="s" s="0">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="12">
@@ -987,12 +1014,14 @@
         <v>21</v>
       </c>
       <c r="N12" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="O12" t="s" s="0">
         <v>25</v>
       </c>
-      <c r="O12" t="s" s="0">
-        <v>45</v>
-      </c>
-      <c r="P12" s="0"/>
+      <c r="P12" t="s" s="0">
+        <v>26</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n" s="0">
@@ -1038,11 +1067,9 @@
         <v>22</v>
       </c>
       <c r="O13" t="s" s="0">
-        <v>23</v>
-      </c>
-      <c r="P13" t="s" s="0">
-        <v>24</v>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="P13" s="0"/>
     </row>
     <row r="14">
       <c r="A14" t="n" s="0">
@@ -1085,14 +1112,110 @@
         <v>21</v>
       </c>
       <c r="N14" t="s" s="0">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="O14" t="s" s="0">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="P14" t="s" s="0">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n" s="0">
+        <v>16.0</v>
+      </c>
+      <c r="B15" t="s" s="0">
+        <v>49</v>
+      </c>
+      <c r="C15" t="n" s="0">
+        <v>1000.0</v>
+      </c>
+      <c r="D15" t="s" s="30">
+        <v>50</v>
+      </c>
+      <c r="E15" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="F15" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="G15" t="s" s="0">
+        <v>18</v>
+      </c>
+      <c r="H15" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="I15" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="J15" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="K15" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="L15" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="M15" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="N15" t="s" s="0">
         <v>24</v>
       </c>
+      <c r="O15" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="P15" s="0"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n" s="0">
+        <v>17.0</v>
+      </c>
+      <c r="B16" t="s" s="0">
+        <v>52</v>
+      </c>
+      <c r="C16" t="n" s="0">
+        <v>1000.0</v>
+      </c>
+      <c r="D16" t="s" s="31">
+        <v>53</v>
+      </c>
+      <c r="E16" t="n" s="0">
+        <v>3.0</v>
+      </c>
+      <c r="F16" t="n" s="0">
+        <v>15.0</v>
+      </c>
+      <c r="G16" t="s" s="0">
+        <v>54</v>
+      </c>
+      <c r="H16" t="s" s="0">
+        <v>55</v>
+      </c>
+      <c r="I16" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="J16" t="s" s="0">
+        <v>51</v>
+      </c>
+      <c r="K16" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="L16" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="M16" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="N16" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="O16" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="P16" s="0"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>

--- a/Course_Output.xlsx
+++ b/Course_Output.xlsx
@@ -778,7 +778,7 @@
         <v>38</v>
       </c>
       <c r="K5" t="n" s="0">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="L5" t="n" s="0">
         <v>1.0</v>
@@ -826,7 +826,7 @@
         <v>42</v>
       </c>
       <c r="K6" t="n" s="0">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="L6" t="n" s="0">
         <v>2.0</v>
@@ -874,7 +874,7 @@
         <v>45</v>
       </c>
       <c r="K7" t="n" s="0">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="L7" t="n" s="0">
         <v>3.0</v>
@@ -1558,7 +1558,7 @@
         <v>91</v>
       </c>
       <c r="K21" t="n" s="0">
-        <v>2.0</v>
+        <v>0.0</v>
       </c>
       <c r="L21" t="n" s="0">
         <v>1.0</v>
